--- a/datos_excel/dim_tipos_producto.xlsx
+++ b/datos_excel/dim_tipos_producto.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="46">
+  <si>
+    <t>codigo_linea</t>
+  </si>
   <si>
     <t>tipo_producto</t>
   </si>
@@ -22,106 +25,133 @@
     <t>familia</t>
   </si>
   <si>
-    <t>categoria</t>
-  </si>
-  <si>
     <t>precio_regular</t>
   </si>
   <si>
     <t>costo_produccion</t>
   </si>
   <si>
+    <t>margen_real_pct</t>
+  </si>
+  <si>
     <t>margen_objetivo_pct</t>
   </si>
   <si>
+    <t>gmroii_real</t>
+  </si>
+  <si>
     <t>vida_semanas</t>
   </si>
   <si>
     <t>es_basico</t>
   </si>
   <si>
+    <t>part_venta_pct</t>
+  </si>
+  <si>
+    <t>part_inv_pct</t>
+  </si>
+  <si>
+    <t>factor_costa</t>
+  </si>
+  <si>
+    <t>factor_frio</t>
+  </si>
+  <si>
     <t>tallas_json</t>
   </si>
   <si>
     <t>temporada_ciclo_sem</t>
   </si>
   <si>
-    <t>Blusa Casual</t>
-  </si>
-  <si>
-    <t>Blusa Formal</t>
-  </si>
-  <si>
-    <t>Pantalón Casual</t>
-  </si>
-  <si>
-    <t>Pantalón Formal</t>
-  </si>
-  <si>
-    <t>Vestido Casual</t>
-  </si>
-  <si>
-    <t>Vestido Fiesta</t>
+    <t>JEA</t>
+  </si>
+  <si>
+    <t>GPT</t>
+  </si>
+  <si>
+    <t>CAM</t>
+  </si>
+  <si>
+    <t>POL</t>
+  </si>
+  <si>
+    <t>BER</t>
+  </si>
+  <si>
+    <t>PAN</t>
+  </si>
+  <si>
+    <t>VES</t>
+  </si>
+  <si>
+    <t>ABR</t>
+  </si>
+  <si>
+    <t>TPI</t>
+  </si>
+  <si>
+    <t>BUZ</t>
+  </si>
+  <si>
+    <t>FAL</t>
+  </si>
+  <si>
+    <t>PIJ</t>
+  </si>
+  <si>
+    <t>Jeans</t>
+  </si>
+  <si>
+    <t>Pantalón</t>
+  </si>
+  <si>
+    <t>Camiseta/Blusa</t>
+  </si>
+  <si>
+    <t>Polo</t>
+  </si>
+  <si>
+    <t>Bermuda</t>
+  </si>
+  <si>
+    <t>Pantaloneta</t>
+  </si>
+  <si>
+    <t>Vestido</t>
+  </si>
+  <si>
+    <t>Abrigo</t>
+  </si>
+  <si>
+    <t>Top/Interior</t>
+  </si>
+  <si>
+    <t>Buzo</t>
   </si>
   <si>
     <t>Falda</t>
   </si>
   <si>
-    <t>Chaqueta Mujer</t>
-  </si>
-  <si>
-    <t>Camiseta Hombre</t>
-  </si>
-  <si>
-    <t>Camisa Hombre</t>
-  </si>
-  <si>
-    <t>Pantalón Hombre</t>
-  </si>
-  <si>
-    <t>Jean Hombre</t>
-  </si>
-  <si>
-    <t>Chaqueta Hombre</t>
-  </si>
-  <si>
-    <t>Conjunto Niño</t>
-  </si>
-  <si>
-    <t>Vestido Niña</t>
+    <t>Pijama</t>
+  </si>
+  <si>
+    <t>Unisex</t>
+  </si>
+  <si>
+    <t>Hombre</t>
   </si>
   <si>
     <t>Mujer</t>
   </si>
   <si>
-    <t>Hombre</t>
-  </si>
-  <si>
-    <t>Niño</t>
-  </si>
-  <si>
-    <t>Parte Superior</t>
-  </si>
-  <si>
-    <t>Parte Inferior</t>
-  </si>
-  <si>
-    <t>Vestido</t>
-  </si>
-  <si>
-    <t>Abrigo</t>
-  </si>
-  <si>
-    <t>Conjunto</t>
-  </si>
-  <si>
-    <t>{'XS': 0.08, 'S': 0.22, 'M': 0.35, 'L': 0.25, 'XL': 0.1}</t>
-  </si>
-  <si>
-    <t>{'S': 0.15, 'M': 0.3, 'L': 0.35, 'XL': 0.15, 'XXL': 0.05}</t>
-  </si>
-  <si>
-    <t>{'2': 0.15, '4': 0.2, '6': 0.25, '8': 0.22, '10': 0.18}</t>
+    <t>{'S': 0.15, 'M': 0.32, 'L': 0.33, 'XL': 0.14, 'XXL': 0.06}</t>
+  </si>
+  <si>
+    <t>{'S': 0.14, 'M': 0.31, 'L': 0.34, 'XL': 0.15, 'XXL': 0.06}</t>
+  </si>
+  <si>
+    <t>{'XS': 0.07, 'S': 0.21, 'M': 0.36, 'L': 0.26, 'XL': 0.1}</t>
   </si>
 </sst>
 </file>
@@ -453,10 +483,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -487,484 +517,622 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
       <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2">
+        <v>169900</v>
+      </c>
+      <c r="E2">
+        <v>87482</v>
+      </c>
+      <c r="F2">
+        <v>48.51</v>
+      </c>
+      <c r="G2">
+        <v>48.51</v>
+      </c>
+      <c r="H2">
+        <v>2.42</v>
+      </c>
+      <c r="I2">
+        <v>52</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>22.64</v>
+      </c>
+      <c r="L2">
+        <v>21.62</v>
+      </c>
+      <c r="M2">
+        <v>1.05</v>
+      </c>
+      <c r="N2">
+        <v>1</v>
+      </c>
+      <c r="O2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3">
+        <v>149900</v>
+      </c>
+      <c r="E3">
+        <v>73181</v>
+      </c>
+      <c r="F3">
+        <v>51.18</v>
+      </c>
+      <c r="G3">
+        <v>51.18</v>
+      </c>
+      <c r="H3">
+        <v>2.72</v>
+      </c>
+      <c r="I3">
+        <v>14</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>18.1</v>
+      </c>
+      <c r="L3">
+        <v>16.79</v>
+      </c>
+      <c r="M3">
+        <v>0.88</v>
+      </c>
+      <c r="N3">
+        <v>1.08</v>
+      </c>
+      <c r="O3" t="s">
+        <v>43</v>
+      </c>
+      <c r="P3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4">
+        <v>89900</v>
+      </c>
+      <c r="E4">
+        <v>44500</v>
+      </c>
+      <c r="F4">
+        <v>50.5</v>
+      </c>
+      <c r="G4">
+        <v>50.5</v>
+      </c>
+      <c r="H4">
+        <v>2.35</v>
+      </c>
+      <c r="I4">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D2">
-        <v>89900</v>
-      </c>
-      <c r="E2">
-        <v>32000</v>
-      </c>
-      <c r="F2">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="G2">
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>16.97</v>
+      </c>
+      <c r="L4">
+        <v>18.11</v>
+      </c>
+      <c r="M4">
+        <v>1.35</v>
+      </c>
+      <c r="N4">
+        <v>0.85</v>
+      </c>
+      <c r="O4" t="s">
+        <v>43</v>
+      </c>
+      <c r="P4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5">
+        <v>79900</v>
+      </c>
+      <c r="E5">
+        <v>39998</v>
+      </c>
+      <c r="F5">
+        <v>49.94</v>
+      </c>
+      <c r="G5">
+        <v>49.94</v>
+      </c>
+      <c r="H5">
+        <v>2.21</v>
+      </c>
+      <c r="I5">
         <v>10</v>
       </c>
-      <c r="H2" t="b">
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>7.83</v>
+      </c>
+      <c r="L5">
+        <v>7.35</v>
+      </c>
+      <c r="M5">
+        <v>1.25</v>
+      </c>
+      <c r="N5">
+        <v>0.88</v>
+      </c>
+      <c r="O5" t="s">
+        <v>44</v>
+      </c>
+      <c r="P5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6">
+        <v>99900</v>
+      </c>
+      <c r="E6">
+        <v>47373</v>
+      </c>
+      <c r="F6">
+        <v>52.58</v>
+      </c>
+      <c r="G6">
+        <v>52.58</v>
+      </c>
+      <c r="H6">
+        <v>3.17</v>
+      </c>
+      <c r="I6">
+        <v>8</v>
+      </c>
+      <c r="J6" t="b">
         <v>0</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K6">
+        <v>6.83</v>
+      </c>
+      <c r="L6">
+        <v>6.13</v>
+      </c>
+      <c r="M6">
+        <v>1.8</v>
+      </c>
+      <c r="N6">
+        <v>0.2</v>
+      </c>
+      <c r="O6" t="s">
+        <v>43</v>
+      </c>
+      <c r="P6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" t="s">
         <v>33</v>
       </c>
-      <c r="J2">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3">
-        <v>129900</v>
-      </c>
-      <c r="E3">
-        <v>48000</v>
-      </c>
-      <c r="F3">
-        <v>63</v>
-      </c>
-      <c r="G3">
-        <v>12</v>
-      </c>
-      <c r="H3" t="b">
+      <c r="C7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7">
+        <v>69900</v>
+      </c>
+      <c r="E7">
+        <v>37928</v>
+      </c>
+      <c r="F7">
+        <v>45.74</v>
+      </c>
+      <c r="G7">
+        <v>45.74</v>
+      </c>
+      <c r="H7">
+        <v>2.25</v>
+      </c>
+      <c r="I7">
+        <v>8</v>
+      </c>
+      <c r="J7" t="b">
         <v>0</v>
       </c>
-      <c r="I3" t="s">
-        <v>33</v>
-      </c>
-      <c r="J3">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4">
-        <v>119900</v>
-      </c>
-      <c r="E4">
-        <v>42000</v>
-      </c>
-      <c r="F4">
-        <v>65</v>
-      </c>
-      <c r="G4">
-        <v>12</v>
-      </c>
-      <c r="H4" t="b">
+      <c r="K7">
+        <v>6.41</v>
+      </c>
+      <c r="L7">
+        <v>7.33</v>
+      </c>
+      <c r="M7">
+        <v>1.9</v>
+      </c>
+      <c r="N7">
+        <v>0.15</v>
+      </c>
+      <c r="O7" t="s">
+        <v>43</v>
+      </c>
+      <c r="P7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8">
+        <v>139900</v>
+      </c>
+      <c r="E8">
+        <v>75686</v>
+      </c>
+      <c r="F8">
+        <v>45.9</v>
+      </c>
+      <c r="G8">
+        <v>45.9</v>
+      </c>
+      <c r="H8">
+        <v>2.3</v>
+      </c>
+      <c r="I8">
+        <v>10</v>
+      </c>
+      <c r="J8" t="b">
         <v>0</v>
       </c>
-      <c r="I4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J4">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5">
-        <v>159900</v>
-      </c>
-      <c r="E5">
-        <v>58000</v>
-      </c>
-      <c r="F5">
-        <v>63.7</v>
-      </c>
-      <c r="G5">
-        <v>14</v>
-      </c>
-      <c r="H5" t="b">
-        <v>0</v>
-      </c>
-      <c r="I5" t="s">
-        <v>33</v>
-      </c>
-      <c r="J5">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6">
-        <v>139900</v>
-      </c>
-      <c r="E6">
-        <v>50000</v>
-      </c>
-      <c r="F6">
-        <v>64.3</v>
-      </c>
-      <c r="G6">
-        <v>10</v>
-      </c>
-      <c r="H6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J6">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7">
-        <v>229900</v>
-      </c>
-      <c r="E7">
-        <v>82000</v>
-      </c>
-      <c r="F7">
-        <v>64.3</v>
-      </c>
-      <c r="G7">
-        <v>8</v>
-      </c>
-      <c r="H7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I7" t="s">
-        <v>33</v>
-      </c>
-      <c r="J7">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8">
-        <v>99900</v>
-      </c>
-      <c r="E8">
-        <v>35000</v>
-      </c>
-      <c r="F8">
-        <v>65</v>
-      </c>
-      <c r="G8">
-        <v>10</v>
-      </c>
-      <c r="H8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J8">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
+      <c r="K8">
+        <v>5.94</v>
+      </c>
+      <c r="L8">
+        <v>5.24</v>
+      </c>
+      <c r="M8">
+        <v>2.2</v>
+      </c>
+      <c r="N8">
+        <v>0.5</v>
+      </c>
+      <c r="O8" t="s">
+        <v>45</v>
+      </c>
+      <c r="P8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="D9">
         <v>189900</v>
       </c>
       <c r="E9">
-        <v>70000</v>
+        <v>111585</v>
       </c>
       <c r="F9">
-        <v>63.1</v>
+        <v>41.24</v>
       </c>
       <c r="G9">
+        <v>41.24</v>
+      </c>
+      <c r="H9">
+        <v>1.51</v>
+      </c>
+      <c r="I9">
         <v>14</v>
       </c>
-      <c r="H9" t="b">
+      <c r="J9" t="b">
         <v>0</v>
       </c>
-      <c r="I9" t="s">
-        <v>33</v>
-      </c>
-      <c r="J9">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
+      <c r="K9">
+        <v>3.42</v>
+      </c>
+      <c r="L9">
+        <v>4.18</v>
+      </c>
+      <c r="M9">
+        <v>0.06</v>
+      </c>
+      <c r="N9">
+        <v>2.4</v>
+      </c>
+      <c r="O9" t="s">
+        <v>43</v>
+      </c>
+      <c r="P9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="D10">
-        <v>69900</v>
+        <v>59900</v>
       </c>
       <c r="E10">
-        <v>24000</v>
+        <v>29105</v>
       </c>
       <c r="F10">
-        <v>65.7</v>
+        <v>51.41</v>
       </c>
       <c r="G10">
+        <v>51.41</v>
+      </c>
+      <c r="H10">
+        <v>2.35</v>
+      </c>
+      <c r="I10">
         <v>10</v>
       </c>
-      <c r="H10" t="b">
-        <v>1</v>
-      </c>
-      <c r="I10" t="s">
-        <v>34</v>
-      </c>
-      <c r="J10">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+      <c r="J10" t="b">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>3.33</v>
+      </c>
+      <c r="L10">
+        <v>4.43</v>
+      </c>
+      <c r="M10">
+        <v>1.3</v>
+      </c>
+      <c r="N10">
+        <v>0.9</v>
+      </c>
+      <c r="O10" t="s">
+        <v>45</v>
+      </c>
+      <c r="P10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="D11">
         <v>119900</v>
       </c>
       <c r="E11">
-        <v>43000</v>
+        <v>64770</v>
       </c>
       <c r="F11">
-        <v>64.09999999999999</v>
+        <v>45.98</v>
       </c>
       <c r="G11">
+        <v>45.98</v>
+      </c>
+      <c r="H11">
+        <v>2.55</v>
+      </c>
+      <c r="I11">
         <v>12</v>
       </c>
-      <c r="H11" t="b">
+      <c r="J11" t="b">
         <v>0</v>
       </c>
-      <c r="I11" t="s">
-        <v>34</v>
-      </c>
-      <c r="J11">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+      <c r="K11">
+        <v>3.11</v>
+      </c>
+      <c r="L11">
+        <v>2.65</v>
+      </c>
+      <c r="M11">
+        <v>0.3</v>
+      </c>
+      <c r="N11">
+        <v>1.8</v>
+      </c>
+      <c r="O11" t="s">
+        <v>43</v>
+      </c>
+      <c r="P11">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="C12" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="D12">
-        <v>149900</v>
+        <v>99900</v>
       </c>
       <c r="E12">
-        <v>54000</v>
+        <v>47762</v>
       </c>
       <c r="F12">
-        <v>64</v>
+        <v>52.19</v>
       </c>
       <c r="G12">
-        <v>14</v>
-      </c>
-      <c r="H12" t="b">
-        <v>1</v>
-      </c>
-      <c r="I12" t="s">
-        <v>34</v>
-      </c>
-      <c r="J12">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+        <v>52.19</v>
+      </c>
+      <c r="H12">
+        <v>2.5</v>
+      </c>
+      <c r="I12">
+        <v>10</v>
+      </c>
+      <c r="J12" t="b">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>2.75</v>
+      </c>
+      <c r="L12">
+        <v>3.09</v>
+      </c>
+      <c r="M12">
+        <v>1.5</v>
+      </c>
+      <c r="N12">
+        <v>0.6</v>
+      </c>
+      <c r="O12" t="s">
+        <v>45</v>
+      </c>
+      <c r="P12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="C13" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="D13">
-        <v>169900</v>
+        <v>89900</v>
       </c>
       <c r="E13">
-        <v>60000</v>
+        <v>46523</v>
       </c>
       <c r="F13">
-        <v>64.7</v>
+        <v>48.25</v>
       </c>
       <c r="G13">
-        <v>16</v>
-      </c>
-      <c r="H13" t="b">
-        <v>1</v>
-      </c>
-      <c r="I13" t="s">
-        <v>34</v>
-      </c>
-      <c r="J13">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" t="s">
-        <v>31</v>
-      </c>
-      <c r="D14">
-        <v>199900</v>
-      </c>
-      <c r="E14">
-        <v>72000</v>
-      </c>
-      <c r="F14">
-        <v>64</v>
-      </c>
-      <c r="G14">
-        <v>14</v>
-      </c>
-      <c r="H14" t="b">
+        <v>48.25</v>
+      </c>
+      <c r="H13">
+        <v>2.95</v>
+      </c>
+      <c r="I13">
+        <v>12</v>
+      </c>
+      <c r="J13" t="b">
         <v>0</v>
       </c>
-      <c r="I14" t="s">
-        <v>34</v>
-      </c>
-      <c r="J14">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15">
-        <v>89900</v>
-      </c>
-      <c r="E15">
-        <v>32000</v>
-      </c>
-      <c r="F15">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="G15">
-        <v>8</v>
-      </c>
-      <c r="H15" t="b">
-        <v>0</v>
-      </c>
-      <c r="I15" t="s">
-        <v>35</v>
-      </c>
-      <c r="J15">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" t="s">
-        <v>27</v>
-      </c>
-      <c r="C16" t="s">
-        <v>30</v>
-      </c>
-      <c r="D16">
-        <v>79900</v>
-      </c>
-      <c r="E16">
-        <v>28000</v>
-      </c>
-      <c r="F16">
-        <v>65</v>
-      </c>
-      <c r="G16">
-        <v>8</v>
-      </c>
-      <c r="H16" t="b">
-        <v>0</v>
-      </c>
-      <c r="I16" t="s">
-        <v>35</v>
-      </c>
-      <c r="J16">
+      <c r="K13">
+        <v>0.37</v>
+      </c>
+      <c r="L13">
+        <v>0.36</v>
+      </c>
+      <c r="M13">
+        <v>1.1</v>
+      </c>
+      <c r="N13">
+        <v>1.05</v>
+      </c>
+      <c r="O13" t="s">
+        <v>43</v>
+      </c>
+      <c r="P13">
         <v>8</v>
       </c>
     </row>

--- a/datos_excel/dim_tipos_producto.xlsx
+++ b/datos_excel/dim_tipos_producto.xlsx
@@ -1,181 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="46">
-  <si>
-    <t>codigo_linea</t>
-  </si>
-  <si>
-    <t>tipo_producto</t>
-  </si>
-  <si>
-    <t>familia</t>
-  </si>
-  <si>
-    <t>precio_regular</t>
-  </si>
-  <si>
-    <t>costo_produccion</t>
-  </si>
-  <si>
-    <t>margen_real_pct</t>
-  </si>
-  <si>
-    <t>margen_objetivo_pct</t>
-  </si>
-  <si>
-    <t>gmroii_real</t>
-  </si>
-  <si>
-    <t>vida_semanas</t>
-  </si>
-  <si>
-    <t>es_basico</t>
-  </si>
-  <si>
-    <t>part_venta_pct</t>
-  </si>
-  <si>
-    <t>part_inv_pct</t>
-  </si>
-  <si>
-    <t>factor_costa</t>
-  </si>
-  <si>
-    <t>factor_frio</t>
-  </si>
-  <si>
-    <t>tallas_json</t>
-  </si>
-  <si>
-    <t>temporada_ciclo_sem</t>
-  </si>
-  <si>
-    <t>JEA</t>
-  </si>
-  <si>
-    <t>GPT</t>
-  </si>
-  <si>
-    <t>CAM</t>
-  </si>
-  <si>
-    <t>POL</t>
-  </si>
-  <si>
-    <t>BER</t>
-  </si>
-  <si>
-    <t>PAN</t>
-  </si>
-  <si>
-    <t>VES</t>
-  </si>
-  <si>
-    <t>ABR</t>
-  </si>
-  <si>
-    <t>TPI</t>
-  </si>
-  <si>
-    <t>BUZ</t>
-  </si>
-  <si>
-    <t>FAL</t>
-  </si>
-  <si>
-    <t>PIJ</t>
-  </si>
-  <si>
-    <t>Jeans</t>
-  </si>
-  <si>
-    <t>Pantalón</t>
-  </si>
-  <si>
-    <t>Camiseta/Blusa</t>
-  </si>
-  <si>
-    <t>Polo</t>
-  </si>
-  <si>
-    <t>Bermuda</t>
-  </si>
-  <si>
-    <t>Pantaloneta</t>
-  </si>
-  <si>
-    <t>Vestido</t>
-  </si>
-  <si>
-    <t>Abrigo</t>
-  </si>
-  <si>
-    <t>Top/Interior</t>
-  </si>
-  <si>
-    <t>Buzo</t>
-  </si>
-  <si>
-    <t>Falda</t>
-  </si>
-  <si>
-    <t>Pijama</t>
-  </si>
-  <si>
-    <t>Unisex</t>
-  </si>
-  <si>
-    <t>Hombre</t>
-  </si>
-  <si>
-    <t>Mujer</t>
-  </si>
-  <si>
-    <t>{'S': 0.15, 'M': 0.32, 'L': 0.33, 'XL': 0.14, 'XXL': 0.06}</t>
-  </si>
-  <si>
-    <t>{'S': 0.14, 'M': 0.31, 'L': 0.34, 'XL': 0.15, 'XXL': 0.06}</t>
-  </si>
-  <si>
-    <t>{'XS': 0.07, 'S': 0.21, 'M': 0.36, 'L': 0.26, 'XL': 0.1}</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -183,18 +45,94 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -482,661 +420,793 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:P13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:16">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" t="s">
-        <v>15</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>codigo_linea</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>tipo_producto</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>familia</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>precio_regular</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>costo_produccion</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>margen_real_pct</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>margen_objetivo_pct</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>gmroii_real</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>vida_semanas</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>es_basico</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>part_venta_pct</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>part_inv_pct</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>factor_costa</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>factor_frio</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>tallas_json</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>temporada_ciclo_sem</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:16">
-      <c r="A2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D2">
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>JEA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Jeans</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
         <v>169900</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>87482</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="n">
         <v>48.51</v>
       </c>
-      <c r="G2">
+      <c r="G2" t="n">
         <v>48.51</v>
       </c>
-      <c r="H2">
+      <c r="H2" t="n">
         <v>2.42</v>
       </c>
-      <c r="I2">
+      <c r="I2" t="n">
         <v>52</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
       </c>
-      <c r="K2">
+      <c r="K2" t="n">
         <v>22.64</v>
       </c>
-      <c r="L2">
+      <c r="L2" t="n">
         <v>21.62</v>
       </c>
-      <c r="M2">
+      <c r="M2" t="n">
         <v>1.05</v>
       </c>
-      <c r="N2">
+      <c r="N2" t="n">
         <v>1</v>
       </c>
-      <c r="O2" t="s">
-        <v>43</v>
-      </c>
-      <c r="P2">
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>{'S': 0.15, 'M': 0.32, 'L': 0.33, 'XL': 0.14, 'XXL': 0.06}</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
-      <c r="A3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D3">
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>GPT</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Pantalón</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
         <v>149900</v>
       </c>
-      <c r="E3">
+      <c r="E3" t="n">
         <v>73181</v>
       </c>
-      <c r="F3">
+      <c r="F3" t="n">
         <v>51.18</v>
       </c>
-      <c r="G3">
+      <c r="G3" t="n">
         <v>51.18</v>
       </c>
-      <c r="H3">
+      <c r="H3" t="n">
         <v>2.72</v>
       </c>
-      <c r="I3">
+      <c r="I3" t="n">
         <v>14</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
       </c>
-      <c r="K3">
+      <c r="K3" t="n">
         <v>18.1</v>
       </c>
-      <c r="L3">
+      <c r="L3" t="n">
         <v>16.79</v>
       </c>
-      <c r="M3">
+      <c r="M3" t="n">
         <v>0.88</v>
       </c>
-      <c r="N3">
+      <c r="N3" t="n">
         <v>1.08</v>
       </c>
-      <c r="O3" t="s">
-        <v>43</v>
-      </c>
-      <c r="P3">
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>{'S': 0.15, 'M': 0.32, 'L': 0.33, 'XL': 0.14, 'XXL': 0.06}</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
-      <c r="A4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D4">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CAM</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Camiseta/Blusa</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
         <v>89900</v>
       </c>
-      <c r="E4">
+      <c r="E4" t="n">
         <v>44500</v>
       </c>
-      <c r="F4">
+      <c r="F4" t="n">
         <v>50.5</v>
       </c>
-      <c r="G4">
+      <c r="G4" t="n">
         <v>50.5</v>
       </c>
-      <c r="H4">
+      <c r="H4" t="n">
         <v>2.35</v>
       </c>
-      <c r="I4">
+      <c r="I4" t="n">
         <v>10</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
       </c>
-      <c r="K4">
+      <c r="K4" t="n">
         <v>16.97</v>
       </c>
-      <c r="L4">
+      <c r="L4" t="n">
         <v>18.11</v>
       </c>
-      <c r="M4">
+      <c r="M4" t="n">
         <v>1.35</v>
       </c>
-      <c r="N4">
+      <c r="N4" t="n">
         <v>0.85</v>
       </c>
-      <c r="O4" t="s">
-        <v>43</v>
-      </c>
-      <c r="P4">
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>{'S': 0.15, 'M': 0.32, 'L': 0.33, 'XL': 0.14, 'XXL': 0.06}</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
-      <c r="A5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D5">
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>POL</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Polo</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Hombre</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
         <v>79900</v>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>39998</v>
       </c>
-      <c r="F5">
+      <c r="F5" t="n">
         <v>49.94</v>
       </c>
-      <c r="G5">
+      <c r="G5" t="n">
         <v>49.94</v>
       </c>
-      <c r="H5">
+      <c r="H5" t="n">
         <v>2.21</v>
       </c>
-      <c r="I5">
+      <c r="I5" t="n">
         <v>10</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
-      <c r="K5">
+      <c r="K5" t="n">
         <v>7.83</v>
       </c>
-      <c r="L5">
+      <c r="L5" t="n">
         <v>7.35</v>
       </c>
-      <c r="M5">
+      <c r="M5" t="n">
         <v>1.25</v>
       </c>
-      <c r="N5">
+      <c r="N5" t="n">
         <v>0.88</v>
       </c>
-      <c r="O5" t="s">
-        <v>44</v>
-      </c>
-      <c r="P5">
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>{'S': 0.14, 'M': 0.31, 'L': 0.34, 'XL': 0.15, 'XXL': 0.06}</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
-      <c r="A6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" t="s">
-        <v>40</v>
-      </c>
-      <c r="D6">
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BER</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Bermuda</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
         <v>99900</v>
       </c>
-      <c r="E6">
+      <c r="E6" t="n">
         <v>47373</v>
       </c>
-      <c r="F6">
+      <c r="F6" t="n">
         <v>52.58</v>
       </c>
-      <c r="G6">
+      <c r="G6" t="n">
         <v>52.58</v>
       </c>
-      <c r="H6">
+      <c r="H6" t="n">
         <v>3.17</v>
       </c>
-      <c r="I6">
+      <c r="I6" t="n">
         <v>8</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
       </c>
-      <c r="K6">
+      <c r="K6" t="n">
         <v>6.83</v>
       </c>
-      <c r="L6">
+      <c r="L6" t="n">
         <v>6.13</v>
       </c>
-      <c r="M6">
+      <c r="M6" t="n">
         <v>1.8</v>
       </c>
-      <c r="N6">
+      <c r="N6" t="n">
         <v>0.2</v>
       </c>
-      <c r="O6" t="s">
-        <v>43</v>
-      </c>
-      <c r="P6">
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>{'S': 0.15, 'M': 0.32, 'L': 0.33, 'XL': 0.14, 'XXL': 0.06}</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:16">
-      <c r="A7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D7">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PAN</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Pantaloneta</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
         <v>69900</v>
       </c>
-      <c r="E7">
+      <c r="E7" t="n">
         <v>37928</v>
       </c>
-      <c r="F7">
+      <c r="F7" t="n">
         <v>45.74</v>
       </c>
-      <c r="G7">
+      <c r="G7" t="n">
         <v>45.74</v>
       </c>
-      <c r="H7">
+      <c r="H7" t="n">
         <v>2.25</v>
       </c>
-      <c r="I7">
+      <c r="I7" t="n">
         <v>8</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
       </c>
-      <c r="K7">
+      <c r="K7" t="n">
         <v>6.41</v>
       </c>
-      <c r="L7">
+      <c r="L7" t="n">
         <v>7.33</v>
       </c>
-      <c r="M7">
+      <c r="M7" t="n">
         <v>1.9</v>
       </c>
-      <c r="N7">
+      <c r="N7" t="n">
         <v>0.15</v>
       </c>
-      <c r="O7" t="s">
-        <v>43</v>
-      </c>
-      <c r="P7">
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>{'S': 0.15, 'M': 0.32, 'L': 0.33, 'XL': 0.14, 'XXL': 0.06}</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:16">
-      <c r="A8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" t="s">
-        <v>42</v>
-      </c>
-      <c r="D8">
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>VES</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Vestido</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
         <v>139900</v>
       </c>
-      <c r="E8">
+      <c r="E8" t="n">
         <v>75686</v>
       </c>
-      <c r="F8">
+      <c r="F8" t="n">
         <v>45.9</v>
       </c>
-      <c r="G8">
+      <c r="G8" t="n">
         <v>45.9</v>
       </c>
-      <c r="H8">
+      <c r="H8" t="n">
         <v>2.3</v>
       </c>
-      <c r="I8">
+      <c r="I8" t="n">
         <v>10</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
       </c>
-      <c r="K8">
+      <c r="K8" t="n">
         <v>5.94</v>
       </c>
-      <c r="L8">
+      <c r="L8" t="n">
         <v>5.24</v>
       </c>
-      <c r="M8">
+      <c r="M8" t="n">
         <v>2.2</v>
       </c>
-      <c r="N8">
+      <c r="N8" t="n">
         <v>0.5</v>
       </c>
-      <c r="O8" t="s">
-        <v>45</v>
-      </c>
-      <c r="P8">
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>{'XS': 0.07, 'S': 0.21, 'M': 0.36, 'L': 0.26, 'XL': 0.1}</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
-      <c r="A9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" t="s">
-        <v>40</v>
-      </c>
-      <c r="D9">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ABR</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Abrigo</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
         <v>189900</v>
       </c>
-      <c r="E9">
+      <c r="E9" t="n">
         <v>111585</v>
       </c>
-      <c r="F9">
+      <c r="F9" t="n">
         <v>41.24</v>
       </c>
-      <c r="G9">
+      <c r="G9" t="n">
         <v>41.24</v>
       </c>
-      <c r="H9">
+      <c r="H9" t="n">
         <v>1.51</v>
       </c>
-      <c r="I9">
+      <c r="I9" t="n">
         <v>14</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
       </c>
-      <c r="K9">
+      <c r="K9" t="n">
         <v>3.42</v>
       </c>
-      <c r="L9">
+      <c r="L9" t="n">
         <v>4.18</v>
       </c>
-      <c r="M9">
+      <c r="M9" t="n">
         <v>0.06</v>
       </c>
-      <c r="N9">
+      <c r="N9" t="n">
         <v>2.4</v>
       </c>
-      <c r="O9" t="s">
-        <v>43</v>
-      </c>
-      <c r="P9">
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>{'S': 0.15, 'M': 0.32, 'L': 0.33, 'XL': 0.14, 'XXL': 0.06}</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:16">
-      <c r="A10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10">
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TPI</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Top/Interior</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
         <v>59900</v>
       </c>
-      <c r="E10">
+      <c r="E10" t="n">
         <v>29105</v>
       </c>
-      <c r="F10">
+      <c r="F10" t="n">
         <v>51.41</v>
       </c>
-      <c r="G10">
+      <c r="G10" t="n">
         <v>51.41</v>
       </c>
-      <c r="H10">
+      <c r="H10" t="n">
         <v>2.35</v>
       </c>
-      <c r="I10">
+      <c r="I10" t="n">
         <v>10</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
       </c>
-      <c r="K10">
+      <c r="K10" t="n">
         <v>3.33</v>
       </c>
-      <c r="L10">
+      <c r="L10" t="n">
         <v>4.43</v>
       </c>
-      <c r="M10">
+      <c r="M10" t="n">
         <v>1.3</v>
       </c>
-      <c r="N10">
+      <c r="N10" t="n">
         <v>0.9</v>
       </c>
-      <c r="O10" t="s">
-        <v>45</v>
-      </c>
-      <c r="P10">
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>{'XS': 0.07, 'S': 0.21, 'M': 0.36, 'L': 0.26, 'XL': 0.1}</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:16">
-      <c r="A11" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11">
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>BUZ</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Buzo</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
         <v>119900</v>
       </c>
-      <c r="E11">
+      <c r="E11" t="n">
         <v>64770</v>
       </c>
-      <c r="F11">
+      <c r="F11" t="n">
         <v>45.98</v>
       </c>
-      <c r="G11">
+      <c r="G11" t="n">
         <v>45.98</v>
       </c>
-      <c r="H11">
+      <c r="H11" t="n">
         <v>2.55</v>
       </c>
-      <c r="I11">
+      <c r="I11" t="n">
         <v>12</v>
       </c>
       <c r="J11" t="b">
         <v>0</v>
       </c>
-      <c r="K11">
+      <c r="K11" t="n">
         <v>3.11</v>
       </c>
-      <c r="L11">
+      <c r="L11" t="n">
         <v>2.65</v>
       </c>
-      <c r="M11">
+      <c r="M11" t="n">
         <v>0.3</v>
       </c>
-      <c r="N11">
+      <c r="N11" t="n">
         <v>1.8</v>
       </c>
-      <c r="O11" t="s">
-        <v>43</v>
-      </c>
-      <c r="P11">
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>{'S': 0.15, 'M': 0.32, 'L': 0.33, 'XL': 0.14, 'XXL': 0.06}</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:16">
-      <c r="A12" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" t="s">
-        <v>38</v>
-      </c>
-      <c r="C12" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12">
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>FAL</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Falda</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Mujer</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>99900</v>
       </c>
-      <c r="E12">
+      <c r="E12" t="n">
         <v>47762</v>
       </c>
-      <c r="F12">
+      <c r="F12" t="n">
         <v>52.19</v>
       </c>
-      <c r="G12">
+      <c r="G12" t="n">
         <v>52.19</v>
       </c>
-      <c r="H12">
+      <c r="H12" t="n">
         <v>2.5</v>
       </c>
-      <c r="I12">
+      <c r="I12" t="n">
         <v>10</v>
       </c>
       <c r="J12" t="b">
         <v>0</v>
       </c>
-      <c r="K12">
+      <c r="K12" t="n">
         <v>2.75</v>
       </c>
-      <c r="L12">
+      <c r="L12" t="n">
         <v>3.09</v>
       </c>
-      <c r="M12">
+      <c r="M12" t="n">
         <v>1.5</v>
       </c>
-      <c r="N12">
+      <c r="N12" t="n">
         <v>0.6</v>
       </c>
-      <c r="O12" t="s">
-        <v>45</v>
-      </c>
-      <c r="P12">
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>{'XS': 0.07, 'S': 0.21, 'M': 0.36, 'L': 0.26, 'XL': 0.1}</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:16">
-      <c r="A13" t="s">
-        <v>27</v>
-      </c>
-      <c r="B13" t="s">
-        <v>39</v>
-      </c>
-      <c r="C13" t="s">
-        <v>40</v>
-      </c>
-      <c r="D13">
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>PIJ</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Pijama</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
         <v>89900</v>
       </c>
-      <c r="E13">
+      <c r="E13" t="n">
         <v>46523</v>
       </c>
-      <c r="F13">
+      <c r="F13" t="n">
         <v>48.25</v>
       </c>
-      <c r="G13">
+      <c r="G13" t="n">
         <v>48.25</v>
       </c>
-      <c r="H13">
+      <c r="H13" t="n">
         <v>2.95</v>
       </c>
-      <c r="I13">
+      <c r="I13" t="n">
         <v>12</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
       </c>
-      <c r="K13">
+      <c r="K13" t="n">
         <v>0.37</v>
       </c>
-      <c r="L13">
+      <c r="L13" t="n">
         <v>0.36</v>
       </c>
-      <c r="M13">
+      <c r="M13" t="n">
         <v>1.1</v>
       </c>
-      <c r="N13">
+      <c r="N13" t="n">
         <v>1.05</v>
       </c>
-      <c r="O13" t="s">
-        <v>43</v>
-      </c>
-      <c r="P13">
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>{'S': 0.15, 'M': 0.32, 'L': 0.33, 'XL': 0.14, 'XXL': 0.06}</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
         <v>8</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>